--- a/src/main/resources/com/company/onboarding/report/list-of-monitor.xlsx
+++ b/src/main/resources/com/company/onboarding/report/list-of-monitor.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shander\OpenideProjects\Onboarding\src\main\resources\com\company\onboarding\report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andrey\OpenideProjects\Onbording\src\main\resources\com\company\onboarding\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F5D71B-DC6C-4B2E-905E-E34925D93125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A63B829-BD95-4FE8-8399-CDBD1621B880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7512" yWindow="6168" windowWidth="25344" windowHeight="15720" xr2:uid="{9DEB9A74-BBFC-4B46-A875-FBCE8E1F0617}"/>
+    <workbookView xWindow="4215" yWindow="3795" windowWidth="21600" windowHeight="11235" xr2:uid="{9DEB9A74-BBFC-4B46-A875-FBCE8E1F0617}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,9 +34,6 @@
     <t>${upperpres}</t>
   </si>
   <si>
-    <t>${lowres}</t>
-  </si>
-  <si>
     <t>${pulse}</t>
   </si>
   <si>
@@ -62,6 +59,9 @@
   </si>
   <si>
     <t>${timeTest}</t>
+  </si>
+  <si>
+    <t>${lowpres}</t>
   </si>
 </sst>
 </file>
@@ -71,7 +71,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="h:mm;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -90,6 +90,13 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="4"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
@@ -130,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -148,6 +155,24 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -466,59 +491,87 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C90D612-D9E5-AB45-B940-529929C227C5}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="1" max="1" width="11.375" customWidth="1"/>
+    <col min="2" max="2" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="7" t="s">
+    </row>
+    <row r="4" spans="1:5" s="1" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>10</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>2</v>
-      </c>
+    </row>
+    <row r="5" spans="1:5" s="1" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+    </row>
+    <row r="6" spans="1:5" s="1" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+    </row>
+    <row r="7" spans="1:5" s="1" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="8"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="11"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/src/main/resources/com/company/onboarding/report/list-of-monitor.xlsx
+++ b/src/main/resources/com/company/onboarding/report/list-of-monitor.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andrey\OpenideProjects\Onbording\src\main\resources\com\company\onboarding\report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shander\OpenideProjects\Onboarding\src\main\resources\com\company\onboarding\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A63B829-BD95-4FE8-8399-CDBD1621B880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5772E4-761E-4314-ABB4-3B4AACE44BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4215" yWindow="3795" windowWidth="21600" windowHeight="11235" xr2:uid="{9DEB9A74-BBFC-4B46-A875-FBCE8E1F0617}"/>
+    <workbookView xWindow="3708" yWindow="840" windowWidth="25344" windowHeight="15720" xr2:uid="{9DEB9A74-BBFC-4B46-A875-FBCE8E1F0617}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Header">Sheet1!$A$1:$E$3</definedName>
-    <definedName name="Mon">Sheet1!$A$4:$E$4</definedName>
+    <definedName name="Header">Sheet1!$A$1:$E$6</definedName>
+    <definedName name="Mon">Sheet1!$A$7:$E$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>${upperpres}</t>
   </si>
@@ -62,6 +62,18 @@
   </si>
   <si>
     <t>${lowpres}</t>
+  </si>
+  <si>
+    <t>${dateFrom}</t>
+  </si>
+  <si>
+    <t>${generatedAt}</t>
+  </si>
+  <si>
+    <t>За период:</t>
+  </si>
+  <si>
+    <t>${dateTo}</t>
   </si>
 </sst>
 </file>
@@ -71,7 +83,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="h:mm;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -101,6 +113,20 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -110,7 +136,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -133,11 +159,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -174,7 +209,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -491,93 +537,128 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C90D612-D9E5-AB45-B940-529929C227C5}">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.375" customWidth="1"/>
-    <col min="2" max="2" width="10.75" customWidth="1"/>
+    <col min="1" max="1" width="11.3984375" customWidth="1"/>
+    <col min="2" max="2" width="13.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="17"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="1" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+    <row r="7" spans="1:5" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C7" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E7" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="1" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="8"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-    </row>
-    <row r="6" spans="1:5" s="1" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="8"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-    </row>
-    <row r="7" spans="1:5" s="1" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="8"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
+    <row r="8" spans="1:5" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A8" s="8"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" spans="1:5" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+    </row>
+    <row r="10" spans="1:5" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A10" s="8"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/main/resources/com/company/onboarding/report/list-of-monitor.xlsx
+++ b/src/main/resources/com/company/onboarding/report/list-of-monitor.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shander\OpenideProjects\Onboarding\src\main\resources\com\company\onboarding\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5772E4-761E-4314-ABB4-3B4AACE44BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{907C46BE-8144-4262-87F4-5FC3218325CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3708" yWindow="840" windowWidth="25344" windowHeight="15720" xr2:uid="{9DEB9A74-BBFC-4B46-A875-FBCE8E1F0617}"/>
+    <workbookView xWindow="40380" yWindow="1650" windowWidth="25350" windowHeight="12090" xr2:uid="{9DEB9A74-BBFC-4B46-A875-FBCE8E1F0617}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Header">Sheet1!$A$1:$E$6</definedName>
-    <definedName name="Mon">Sheet1!$A$7:$E$7</definedName>
+    <definedName name="Header">Sheet1!$A$1:$F$6</definedName>
+    <definedName name="Mon">Sheet1!$A$7:$F$7</definedName>
+    <definedName name="MonTrailer">Sheet1!$A$8:$F$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>${upperpres}</t>
   </si>
@@ -74,6 +75,30 @@
   </si>
   <si>
     <t>${dateTo}</t>
+  </si>
+  <si>
+    <t>№</t>
+  </si>
+  <si>
+    <t>${rowNum}</t>
+  </si>
+  <si>
+    <t>${rowCount}</t>
+  </si>
+  <si>
+    <t>Всего:</t>
+  </si>
+  <si>
+    <t>Среднее:</t>
+  </si>
+  <si>
+    <t>${avgUpperPres}</t>
+  </si>
+  <si>
+    <t>${avgLowPres}</t>
+  </si>
+  <si>
+    <t>${avgPulse}</t>
   </si>
 </sst>
 </file>
@@ -172,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -191,14 +216,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -211,6 +230,13 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -222,6 +248,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -537,126 +566,132 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C90D612-D9E5-AB45-B940-529929C227C5}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" customWidth="1"/>
-    <col min="2" max="2" width="13.59765625" customWidth="1"/>
+    <col min="1" max="1" width="7.8984375" customWidth="1"/>
+    <col min="2" max="2" width="11.3984375" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
+      <c r="D2" s="1"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B3" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="C3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="17" t="s">
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="17"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
+      <c r="F4" s="18"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="2"/>
+      <c r="C5" s="19"/>
       <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:6" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="E7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="F7" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-    </row>
-    <row r="9" spans="1:5" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-    </row>
-    <row r="10" spans="1:5" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
+    <row r="8" spans="1:6" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B10" s="9"/>
       <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/src/main/resources/com/company/onboarding/report/list-of-monitor.xlsx
+++ b/src/main/resources/com/company/onboarding/report/list-of-monitor.xlsx
@@ -5,20 +5,22 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shander\OpenideProjects\Onboarding\src\main\resources\com\company\onboarding\report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andrey\OpenideProjects\Onbording\src\main\resources\com\company\onboarding\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{907C46BE-8144-4262-87F4-5FC3218325CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828F06FD-7AE6-4CBD-B7D3-8644011ACA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40380" yWindow="1650" windowWidth="25350" windowHeight="12090" xr2:uid="{9DEB9A74-BBFC-4B46-A875-FBCE8E1F0617}"/>
+    <workbookView xWindow="5790" yWindow="3315" windowWidth="21600" windowHeight="11235" xr2:uid="{9DEB9A74-BBFC-4B46-A875-FBCE8E1F0617}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Header">Sheet1!$A$1:$F$6</definedName>
-    <definedName name="Mon">Sheet1!$A$7:$F$7</definedName>
-    <definedName name="MonTrailer">Sheet1!$A$8:$F$8</definedName>
+    <definedName name="Header">Sheet1!$B$1:$G$7</definedName>
+    <definedName name="HeaderUsers">Sheet1!$A$10:$G$11</definedName>
+    <definedName name="Mon">Sheet1!$B$8:$G$8</definedName>
+    <definedName name="MonTrailer">Sheet1!$B$9:$G$9</definedName>
+    <definedName name="Users">Sheet1!$C$13:$G$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>${upperpres}</t>
   </si>
@@ -38,9 +40,6 @@
     <t>${pulse}</t>
   </si>
   <si>
-    <t>Журнал контроля показаний давления</t>
-  </si>
-  <si>
     <t>Дата</t>
   </si>
   <si>
@@ -65,18 +64,12 @@
     <t>${lowpres}</t>
   </si>
   <si>
-    <t>${dateFrom}</t>
-  </si>
-  <si>
     <t>${generatedAt}</t>
   </si>
   <si>
     <t>За период:</t>
   </si>
   <si>
-    <t>${dateTo}</t>
-  </si>
-  <si>
     <t>№</t>
   </si>
   <si>
@@ -99,6 +92,39 @@
   </si>
   <si>
     <t>${avgPulse}</t>
+  </si>
+  <si>
+    <t>${dateFrom} - ${dateTo}</t>
+  </si>
+  <si>
+    <t>${user}</t>
+  </si>
+  <si>
+    <t>Пациент:</t>
+  </si>
+  <si>
+    <t>Журнал контроля давления.</t>
+  </si>
+  <si>
+    <t>Список пользователей:</t>
+  </si>
+  <si>
+    <t>Пользователь</t>
+  </si>
+  <si>
+    <t>Имя</t>
+  </si>
+  <si>
+    <t>Фамилия</t>
+  </si>
+  <si>
+    <t>${username}</t>
+  </si>
+  <si>
+    <t>${firstName}</t>
+  </si>
+  <si>
+    <t>${lastName}</t>
   </si>
 </sst>
 </file>
@@ -108,7 +134,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="h:mm;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -132,21 +158,51 @@
       <charset val="204"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="4"/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -197,7 +253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -213,44 +269,37 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -566,132 +615,168 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C90D612-D9E5-AB45-B940-529929C227C5}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:G13"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.8984375" customWidth="1"/>
-    <col min="2" max="2" width="11.3984375" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" customWidth="1"/>
+    <col min="1" max="1" width="3.375" customWidth="1"/>
+    <col min="2" max="2" width="4.75" customWidth="1"/>
+    <col min="3" max="3" width="11.375" customWidth="1"/>
+    <col min="4" max="4" width="6.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B1" s="17" t="s">
+    <row r="2" spans="2:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B2" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C6" s="2"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+    </row>
+    <row r="7" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B3" s="13" t="s">
+      <c r="D7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" s="1" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="13" t="s">
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" s="1" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="18"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="2"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-    </row>
-    <row r="6" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="E9" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="G9" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="9"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C11" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C12" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="15"/>
+      <c r="F12" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="16"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C13" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
+  <mergeCells count="9">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
